--- a/etf_holdings/2026-08-31_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-31_common_daily_changes_summary.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -469,54 +469,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(8,000)</t>
+          <t>00985A(100,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-30,000)、00982A(-2,000)、00405A(-145,000)</t>
+          <t>00981A(-800,000)、00982A(-6,000)、00992A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00981A(-800,000)、00982A(-6,000)、00992A(全數賣出)</t>
+          <t>00982A(-1,000)、00985A(-4,000)、00992A(-25,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -534,19 +534,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00982A(-1,000)、00985A(-4,000)、00992A(-25,000)</t>
+          <t>00981A(-250,000)、00403A(-100,000)、00992A(-190,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(15,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00981A(-250,000)、00403A(-100,000)、00992A(-190,000)</t>
+          <t>00981A(-50,000)、00982A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00985A(15,000)</t>
+          <t>00985A(17,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00981A(-50,000)、00982A(-2,000)</t>
+          <t>00981A(-60,000)、00992A(-121,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -619,24 +619,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00985A(17,000)</t>
+          <t>00403A(50,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00981A(-60,000)、00992A(-121,000)</t>
+          <t>00982A(-1,000)、00985A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00403A(50,000)</t>
+          <t>00985A(8,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00982A(-1,000)、00985A(-8,000)</t>
+          <t>00981A(-30,000)、00982A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -679,54 +679,54 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00403A(28,000)</t>
+          <t>00985A(77,000)、00992A(339,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00981A(-10,000)、00405A(-57,000)</t>
+          <t>00981A(-150,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00985A(77,000)、00992A(339,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00981A(-150,000)</t>
+          <t>00981A(-400,000)、00982A(-27,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -734,29 +734,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(23,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00981A(-400,000)、00982A(-27,000)</t>
+          <t>00981A(-10,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -769,24 +769,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00985A(23,000)</t>
+          <t>00985A(14,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00981A(-10,000)</t>
+          <t>00981A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -794,29 +794,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>00985A(14,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>00981A(-100,000)</t>
+          <t>00982A(-10,000)、00985A(-233,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -824,29 +824,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>00981A(150,000)、00403A(新納入)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>00982A(-10,000)、00985A(-233,000)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -854,29 +854,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00981A(150,000)、00403A(新納入)</t>
+          <t>00403A(186,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00982A(-7,000)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -889,12 +889,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00403A(186,000)</t>
+          <t>00403A(28,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>00982A(-7,000)</t>
+          <t>00981A(-10,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-31_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-31_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,42 +451,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-800,000)、00982A(-6,000)、00992A(全數賣出)</t>
+          <t>00982A(-1,000)、00985A(-4,000)、00992A(-25,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(50,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00982A(-1,000)、00985A(-4,000)、00992A(-25,000)</t>
+          <t>00982A(-1,000)、00985A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,29 +524,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(8,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00981A(-250,000)、00403A(-100,000)、00992A(-190,000)</t>
+          <t>00982A(-2,000)、00405A(-145,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,88 +559,88 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00985A(15,000)</t>
+          <t>00985A(100,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00981A(-50,000)、00982A(-2,000)</t>
+          <t>00982A(-6,000)、00992A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00985A(17,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00981A(-60,000)、00992A(-121,000)</t>
+          <t>00403A(-100,000)、00992A(-190,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00403A(50,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00982A(-1,000)、00985A(-8,000)</t>
+          <t>00982A(-10,000)、00985A(-233,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -649,28 +649,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00985A(8,000)</t>
+          <t>00985A(15,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00981A(-30,000)、00982A(-2,000)</t>
+          <t>00982A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -679,24 +679,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00985A(77,000)、00992A(339,000)</t>
+          <t>00985A(17,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00981A(-150,000)</t>
+          <t>00992A(-121,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -704,29 +704,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(186,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00981A(-400,000)、00982A(-27,000)</t>
+          <t>00982A(-7,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,24 +739,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00985A(23,000)</t>
+          <t>00403A(28,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00981A(-10,000)</t>
+          <t>00405A(-57,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,227 +764,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00985A(14,000)</t>
+          <t>00985A(77,000)、00992A(339,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00981A(-100,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00982A(-10,000)、00985A(-233,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>00981A(150,000)、00403A(新納入)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00403A(186,000)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>00982A(-7,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>00403A(28,000)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>00981A(-10,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>00985A(86,000)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>00981A(-80,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>00981A(-80,000)、00985A(-41,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>00981A(-100,000)、00982A(-2,000)</t>
         </is>
       </c>
     </row>
